--- a/output/pdf_financials_xlsx/JADE.xlsx
+++ b/output/pdf_financials_xlsx/JADE.xlsx
@@ -1313,13 +1313,13 @@
         <v>-0.660191</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.300148</v>
+        <v>-0.300148</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.21404</v>
+        <v>-0.21404</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.108193</v>
+        <v>-0.108193</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.133991</v>
@@ -1597,13 +1597,13 @@
         <v>-0.660191</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.300148</v>
+        <v>-0.300148</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.21404</v>
+        <v>-0.21404</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.108193</v>
+        <v>-0.108193</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.133991</v>
@@ -1777,13 +1777,13 @@
         <v>-0.660191</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.300148</v>
+        <v>-0.300148</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.21404</v>
+        <v>-0.21404</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.108193</v>
+        <v>-0.108193</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.133991</v>
@@ -2037,13 +2037,13 @@
         <v>-0.660191</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.300148</v>
+        <v>-0.300148</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.21404</v>
+        <v>-0.21404</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.108193</v>
+        <v>-0.108193</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.133991</v>
@@ -2157,13 +2157,13 @@
         <v>-0.660191</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.300148</v>
+        <v>-0.300148</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.21404</v>
+        <v>-0.21404</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.108193</v>
+        <v>-0.108193</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.133991</v>
@@ -2299,13 +2299,13 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -5747,31 +5747,31 @@
         <v>0.989765</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.096765</v>
+        <v>1.189765</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.103765</v>
+        <v>1.437559</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.463945</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.528944</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.890127</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.891327</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.034622</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.430985</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.110524</v>
       </c>
       <c r="L92" s="1" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.676368</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.71038</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.71038</v>
       </c>
     </row>
     <row r="93">
@@ -6105,13 +6105,13 @@
         <v>-0.660191</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.300148</v>
+        <v>-0.300148</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.21404</v>
+        <v>-0.21404</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>0.108193</v>
+        <v>-0.108193</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-0.133991</v>
@@ -9660,7 +9660,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -27931,13 +27935,13 @@
         <v>-0.660191</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>0.300148</v>
+        <v>-0.300148</v>
       </c>
       <c r="J226" s="5" t="n">
-        <v>0.21404</v>
+        <v>-0.21404</v>
       </c>
       <c r="K226" s="5" t="n">
-        <v>0.108193</v>
+        <v>-0.108193</v>
       </c>
       <c r="L226" s="5" t="n">
         <v>-0.133991</v>

--- a/output/pdf_financials_xlsx/JADE.xlsx
+++ b/output/pdf_financials_xlsx/JADE.xlsx
@@ -2453,13 +2453,13 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.204953</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.027004</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.406255</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.136618</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.07520499999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.11309</v>
       </c>
     </row>
     <row r="35">
@@ -2565,13 +2565,13 @@
         <v>1e-06</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1e-06</v>
+        <v>0.204954</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.027004</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.406255</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.00292</v>
+        <v>0.139538</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.07520499999999999</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.11309</v>
       </c>
     </row>
     <row r="37">
@@ -3237,13 +3237,13 @@
         <v>0.050694</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.2176</v>
+        <v>0.012647</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.04679</v>
+        <v>0.019786</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.426204</v>
+        <v>0.019949</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -3256,13 +3256,13 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.161141</v>
+        <v>0.024523</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.098604</v>
+        <v>0.023399</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.136884</v>
+        <v>0.023794</v>
       </c>
     </row>
     <row r="49">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
